--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_01-10-2025.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_01-10-2025.xlsx
@@ -528,17 +528,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£10.45</t>
+          <t>£10.35</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£10.45</t>
+          <t>£10.35</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£10.45</t>
+          <t>£10.35</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -576,25 +576,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff69a3d1eb5+80197]
-	GetHandleVerifier [0x0x7ff69a3d1f10+80288]
-	(No symbol) [0x0x7ff69a1502fa]
-	(No symbol) [0x0x7ff69a1a7cd7]
-	(No symbol) [0x0x7ff69a1a7f9c]
-	(No symbol) [0x0x7ff69a1fba87]
-	(No symbol) [0x0x7ff69a1d03bf]
-	(No symbol) [0x0x7ff69a1f87fb]
-	(No symbol) [0x0x7ff69a1d0153]
-	(No symbol) [0x0x7ff69a198b02]
-	(No symbol) [0x0x7ff69a1998d3]
-	GetHandleVerifier [0x0x7ff69a68e83d+2949837]
-	GetHandleVerifier [0x0x7ff69a688c6a+2926330]
-	GetHandleVerifier [0x0x7ff69a6a86c7+3055959]
-	GetHandleVerifier [0x0x7ff69a3ecfee+191102]
-	GetHandleVerifier [0x0x7ff69a3f50af+224063]
-	GetHandleVerifier [0x0x7ff69a3daf64+117236]
-	GetHandleVerifier [0x0x7ff69a3db119+117673]
-	GetHandleVerifier [0x0x7ff69a3c10a8+11064]
+	GetHandleVerifier [0x0x7ff7eb771eb5+80197]
+	GetHandleVerifier [0x0x7ff7eb771f10+80288]
+	(No symbol) [0x0x7ff7eb4f02fa]
+	(No symbol) [0x0x7ff7eb547cd7]
+	(No symbol) [0x0x7ff7eb547f9c]
+	(No symbol) [0x0x7ff7eb59ba87]
+	(No symbol) [0x0x7ff7eb5703bf]
+	(No symbol) [0x0x7ff7eb5987fb]
+	(No symbol) [0x0x7ff7eb570153]
+	(No symbol) [0x0x7ff7eb538b02]
+	(No symbol) [0x0x7ff7eb5398d3]
+	GetHandleVerifier [0x0x7ff7eba2e83d+2949837]
+	GetHandleVerifier [0x0x7ff7eba28c6a+2926330]
+	GetHandleVerifier [0x0x7ff7eba486c7+3055959]
+	GetHandleVerifier [0x0x7ff7eb78cfee+191102]
+	GetHandleVerifier [0x0x7ff7eb7950af+224063]
+	GetHandleVerifier [0x0x7ff7eb77af64+117236]
+	GetHandleVerifier [0x0x7ff7eb77b119+117673]
+	GetHandleVerifier [0x0x7ff7eb7610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -639,17 +639,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£11.97</t>
+          <t>£11.80</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£11.97</t>
+          <t>£11.80</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£11.97</t>
+          <t>£11.80</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -687,25 +687,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff69a3d1eb5+80197]
-	GetHandleVerifier [0x0x7ff69a3d1f10+80288]
-	(No symbol) [0x0x7ff69a1502fa]
-	(No symbol) [0x0x7ff69a1a7cd7]
-	(No symbol) [0x0x7ff69a1a7f9c]
-	(No symbol) [0x0x7ff69a1fba87]
-	(No symbol) [0x0x7ff69a1d03bf]
-	(No symbol) [0x0x7ff69a1f87fb]
-	(No symbol) [0x0x7ff69a1d0153]
-	(No symbol) [0x0x7ff69a198b02]
-	(No symbol) [0x0x7ff69a1998d3]
-	GetHandleVerifier [0x0x7ff69a68e83d+2949837]
-	GetHandleVerifier [0x0x7ff69a688c6a+2926330]
-	GetHandleVerifier [0x0x7ff69a6a86c7+3055959]
-	GetHandleVerifier [0x0x7ff69a3ecfee+191102]
-	GetHandleVerifier [0x0x7ff69a3f50af+224063]
-	GetHandleVerifier [0x0x7ff69a3daf64+117236]
-	GetHandleVerifier [0x0x7ff69a3db119+117673]
-	GetHandleVerifier [0x0x7ff69a3c10a8+11064]
+	GetHandleVerifier [0x0x7ff7eb771eb5+80197]
+	GetHandleVerifier [0x0x7ff7eb771f10+80288]
+	(No symbol) [0x0x7ff7eb4f02fa]
+	(No symbol) [0x0x7ff7eb547cd7]
+	(No symbol) [0x0x7ff7eb547f9c]
+	(No symbol) [0x0x7ff7eb59ba87]
+	(No symbol) [0x0x7ff7eb5703bf]
+	(No symbol) [0x0x7ff7eb5987fb]
+	(No symbol) [0x0x7ff7eb570153]
+	(No symbol) [0x0x7ff7eb538b02]
+	(No symbol) [0x0x7ff7eb5398d3]
+	GetHandleVerifier [0x0x7ff7eba2e83d+2949837]
+	GetHandleVerifier [0x0x7ff7eba28c6a+2926330]
+	GetHandleVerifier [0x0x7ff7eba486c7+3055959]
+	GetHandleVerifier [0x0x7ff7eb78cfee+191102]
+	GetHandleVerifier [0x0x7ff7eb7950af+224063]
+	GetHandleVerifier [0x0x7ff7eb77af64+117236]
+	GetHandleVerifier [0x0x7ff7eb77b119+117673]
+	GetHandleVerifier [0x0x7ff7eb7610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -750,17 +750,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£15.25</t>
+          <t>£15.10</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£15.25</t>
+          <t>£15.10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£15.25</t>
+          <t>£15.10</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -798,25 +798,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff69a3d1eb5+80197]
-	GetHandleVerifier [0x0x7ff69a3d1f10+80288]
-	(No symbol) [0x0x7ff69a1502fa]
-	(No symbol) [0x0x7ff69a1a7cd7]
-	(No symbol) [0x0x7ff69a1a7f9c]
-	(No symbol) [0x0x7ff69a1fba87]
-	(No symbol) [0x0x7ff69a1d03bf]
-	(No symbol) [0x0x7ff69a1f87fb]
-	(No symbol) [0x0x7ff69a1d0153]
-	(No symbol) [0x0x7ff69a198b02]
-	(No symbol) [0x0x7ff69a1998d3]
-	GetHandleVerifier [0x0x7ff69a68e83d+2949837]
-	GetHandleVerifier [0x0x7ff69a688c6a+2926330]
-	GetHandleVerifier [0x0x7ff69a6a86c7+3055959]
-	GetHandleVerifier [0x0x7ff69a3ecfee+191102]
-	GetHandleVerifier [0x0x7ff69a3f50af+224063]
-	GetHandleVerifier [0x0x7ff69a3daf64+117236]
-	GetHandleVerifier [0x0x7ff69a3db119+117673]
-	GetHandleVerifier [0x0x7ff69a3c10a8+11064]
+	GetHandleVerifier [0x0x7ff7eb771eb5+80197]
+	GetHandleVerifier [0x0x7ff7eb771f10+80288]
+	(No symbol) [0x0x7ff7eb4f02fa]
+	(No symbol) [0x0x7ff7eb547cd7]
+	(No symbol) [0x0x7ff7eb547f9c]
+	(No symbol) [0x0x7ff7eb59ba87]
+	(No symbol) [0x0x7ff7eb5703bf]
+	(No symbol) [0x0x7ff7eb5987fb]
+	(No symbol) [0x0x7ff7eb570153]
+	(No symbol) [0x0x7ff7eb538b02]
+	(No symbol) [0x0x7ff7eb5398d3]
+	GetHandleVerifier [0x0x7ff7eba2e83d+2949837]
+	GetHandleVerifier [0x0x7ff7eba28c6a+2926330]
+	GetHandleVerifier [0x0x7ff7eba486c7+3055959]
+	GetHandleVerifier [0x0x7ff7eb78cfee+191102]
+	GetHandleVerifier [0x0x7ff7eb7950af+224063]
+	GetHandleVerifier [0x0x7ff7eb77af64+117236]
+	GetHandleVerifier [0x0x7ff7eb77b119+117673]
+	GetHandleVerifier [0x0x7ff7eb7610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -861,17 +861,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£15.50</t>
+          <t>£15.40</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£15.50</t>
+          <t>£15.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£15.50</t>
+          <t>£15.40</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -909,25 +909,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff69a3d1eb5+80197]
-	GetHandleVerifier [0x0x7ff69a3d1f10+80288]
-	(No symbol) [0x0x7ff69a1502fa]
-	(No symbol) [0x0x7ff69a1a7cd7]
-	(No symbol) [0x0x7ff69a1a7f9c]
-	(No symbol) [0x0x7ff69a1fba87]
-	(No symbol) [0x0x7ff69a1d03bf]
-	(No symbol) [0x0x7ff69a1f87fb]
-	(No symbol) [0x0x7ff69a1d0153]
-	(No symbol) [0x0x7ff69a198b02]
-	(No symbol) [0x0x7ff69a1998d3]
-	GetHandleVerifier [0x0x7ff69a68e83d+2949837]
-	GetHandleVerifier [0x0x7ff69a688c6a+2926330]
-	GetHandleVerifier [0x0x7ff69a6a86c7+3055959]
-	GetHandleVerifier [0x0x7ff69a3ecfee+191102]
-	GetHandleVerifier [0x0x7ff69a3f50af+224063]
-	GetHandleVerifier [0x0x7ff69a3daf64+117236]
-	GetHandleVerifier [0x0x7ff69a3db119+117673]
-	GetHandleVerifier [0x0x7ff69a3c10a8+11064]
+	GetHandleVerifier [0x0x7ff7eb771eb5+80197]
+	GetHandleVerifier [0x0x7ff7eb771f10+80288]
+	(No symbol) [0x0x7ff7eb4f02fa]
+	(No symbol) [0x0x7ff7eb547cd7]
+	(No symbol) [0x0x7ff7eb547f9c]
+	(No symbol) [0x0x7ff7eb59ba87]
+	(No symbol) [0x0x7ff7eb5703bf]
+	(No symbol) [0x0x7ff7eb5987fb]
+	(No symbol) [0x0x7ff7eb570153]
+	(No symbol) [0x0x7ff7eb538b02]
+	(No symbol) [0x0x7ff7eb5398d3]
+	GetHandleVerifier [0x0x7ff7eba2e83d+2949837]
+	GetHandleVerifier [0x0x7ff7eba28c6a+2926330]
+	GetHandleVerifier [0x0x7ff7eba486c7+3055959]
+	GetHandleVerifier [0x0x7ff7eb78cfee+191102]
+	GetHandleVerifier [0x0x7ff7eb7950af+224063]
+	GetHandleVerifier [0x0x7ff7eb77af64+117236]
+	GetHandleVerifier [0x0x7ff7eb77b119+117673]
+	GetHandleVerifier [0x0x7ff7eb7610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -972,17 +972,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£19.80</t>
+          <t>£19.60</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£19.80</t>
+          <t>£19.60</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£19.80</t>
+          <t>£19.60</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1020,25 +1020,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff69a3d1eb5+80197]
-	GetHandleVerifier [0x0x7ff69a3d1f10+80288]
-	(No symbol) [0x0x7ff69a1502fa]
-	(No symbol) [0x0x7ff69a1a7cd7]
-	(No symbol) [0x0x7ff69a1a7f9c]
-	(No symbol) [0x0x7ff69a1fba87]
-	(No symbol) [0x0x7ff69a1d03bf]
-	(No symbol) [0x0x7ff69a1f87fb]
-	(No symbol) [0x0x7ff69a1d0153]
-	(No symbol) [0x0x7ff69a198b02]
-	(No symbol) [0x0x7ff69a1998d3]
-	GetHandleVerifier [0x0x7ff69a68e83d+2949837]
-	GetHandleVerifier [0x0x7ff69a688c6a+2926330]
-	GetHandleVerifier [0x0x7ff69a6a86c7+3055959]
-	GetHandleVerifier [0x0x7ff69a3ecfee+191102]
-	GetHandleVerifier [0x0x7ff69a3f50af+224063]
-	GetHandleVerifier [0x0x7ff69a3daf64+117236]
-	GetHandleVerifier [0x0x7ff69a3db119+117673]
-	GetHandleVerifier [0x0x7ff69a3c10a8+11064]
+	GetHandleVerifier [0x0x7ff7eb771eb5+80197]
+	GetHandleVerifier [0x0x7ff7eb771f10+80288]
+	(No symbol) [0x0x7ff7eb4f02fa]
+	(No symbol) [0x0x7ff7eb547cd7]
+	(No symbol) [0x0x7ff7eb547f9c]
+	(No symbol) [0x0x7ff7eb59ba87]
+	(No symbol) [0x0x7ff7eb5703bf]
+	(No symbol) [0x0x7ff7eb5987fb]
+	(No symbol) [0x0x7ff7eb570153]
+	(No symbol) [0x0x7ff7eb538b02]
+	(No symbol) [0x0x7ff7eb5398d3]
+	GetHandleVerifier [0x0x7ff7eba2e83d+2949837]
+	GetHandleVerifier [0x0x7ff7eba28c6a+2926330]
+	GetHandleVerifier [0x0x7ff7eba486c7+3055959]
+	GetHandleVerifier [0x0x7ff7eb78cfee+191102]
+	GetHandleVerifier [0x0x7ff7eb7950af+224063]
+	GetHandleVerifier [0x0x7ff7eb77af64+117236]
+	GetHandleVerifier [0x0x7ff7eb77b119+117673]
+	GetHandleVerifier [0x0x7ff7eb7610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£21.70</t>
+          <t>£21.45</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£21.70</t>
+          <t>£21.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£21.70</t>
+          <t>£21.45</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1131,25 +1131,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff69a3d1eb5+80197]
-	GetHandleVerifier [0x0x7ff69a3d1f10+80288]
-	(No symbol) [0x0x7ff69a1502fa]
-	(No symbol) [0x0x7ff69a1a7cd7]
-	(No symbol) [0x0x7ff69a1a7f9c]
-	(No symbol) [0x0x7ff69a1fba87]
-	(No symbol) [0x0x7ff69a1d03bf]
-	(No symbol) [0x0x7ff69a1f87fb]
-	(No symbol) [0x0x7ff69a1d0153]
-	(No symbol) [0x0x7ff69a198b02]
-	(No symbol) [0x0x7ff69a1998d3]
-	GetHandleVerifier [0x0x7ff69a68e83d+2949837]
-	GetHandleVerifier [0x0x7ff69a688c6a+2926330]
-	GetHandleVerifier [0x0x7ff69a6a86c7+3055959]
-	GetHandleVerifier [0x0x7ff69a3ecfee+191102]
-	GetHandleVerifier [0x0x7ff69a3f50af+224063]
-	GetHandleVerifier [0x0x7ff69a3daf64+117236]
-	GetHandleVerifier [0x0x7ff69a3db119+117673]
-	GetHandleVerifier [0x0x7ff69a3c10a8+11064]
+	GetHandleVerifier [0x0x7ff7eb771eb5+80197]
+	GetHandleVerifier [0x0x7ff7eb771f10+80288]
+	(No symbol) [0x0x7ff7eb4f02fa]
+	(No symbol) [0x0x7ff7eb547cd7]
+	(No symbol) [0x0x7ff7eb547f9c]
+	(No symbol) [0x0x7ff7eb59ba87]
+	(No symbol) [0x0x7ff7eb5703bf]
+	(No symbol) [0x0x7ff7eb5987fb]
+	(No symbol) [0x0x7ff7eb570153]
+	(No symbol) [0x0x7ff7eb538b02]
+	(No symbol) [0x0x7ff7eb5398d3]
+	GetHandleVerifier [0x0x7ff7eba2e83d+2949837]
+	GetHandleVerifier [0x0x7ff7eba28c6a+2926330]
+	GetHandleVerifier [0x0x7ff7eba486c7+3055959]
+	GetHandleVerifier [0x0x7ff7eb78cfee+191102]
+	GetHandleVerifier [0x0x7ff7eb7950af+224063]
+	GetHandleVerifier [0x0x7ff7eb77af64+117236]
+	GetHandleVerifier [0x0x7ff7eb77b119+117673]
+	GetHandleVerifier [0x0x7ff7eb7610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1194,17 +1194,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£21.90</t>
+          <t>£21.60</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£21.90</t>
+          <t>£21.60</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£21.90</t>
+          <t>£21.60</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1242,25 +1242,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff69a3d1eb5+80197]
-	GetHandleVerifier [0x0x7ff69a3d1f10+80288]
-	(No symbol) [0x0x7ff69a1502fa]
-	(No symbol) [0x0x7ff69a1a7cd7]
-	(No symbol) [0x0x7ff69a1a7f9c]
-	(No symbol) [0x0x7ff69a1fba87]
-	(No symbol) [0x0x7ff69a1d03bf]
-	(No symbol) [0x0x7ff69a1f87fb]
-	(No symbol) [0x0x7ff69a1d0153]
-	(No symbol) [0x0x7ff69a198b02]
-	(No symbol) [0x0x7ff69a1998d3]
-	GetHandleVerifier [0x0x7ff69a68e83d+2949837]
-	GetHandleVerifier [0x0x7ff69a688c6a+2926330]
-	GetHandleVerifier [0x0x7ff69a6a86c7+3055959]
-	GetHandleVerifier [0x0x7ff69a3ecfee+191102]
-	GetHandleVerifier [0x0x7ff69a3f50af+224063]
-	GetHandleVerifier [0x0x7ff69a3daf64+117236]
-	GetHandleVerifier [0x0x7ff69a3db119+117673]
-	GetHandleVerifier [0x0x7ff69a3c10a8+11064]
+	GetHandleVerifier [0x0x7ff7eb771eb5+80197]
+	GetHandleVerifier [0x0x7ff7eb771f10+80288]
+	(No symbol) [0x0x7ff7eb4f02fa]
+	(No symbol) [0x0x7ff7eb547cd7]
+	(No symbol) [0x0x7ff7eb547f9c]
+	(No symbol) [0x0x7ff7eb59ba87]
+	(No symbol) [0x0x7ff7eb5703bf]
+	(No symbol) [0x0x7ff7eb5987fb]
+	(No symbol) [0x0x7ff7eb570153]
+	(No symbol) [0x0x7ff7eb538b02]
+	(No symbol) [0x0x7ff7eb5398d3]
+	GetHandleVerifier [0x0x7ff7eba2e83d+2949837]
+	GetHandleVerifier [0x0x7ff7eba28c6a+2926330]
+	GetHandleVerifier [0x0x7ff7eba486c7+3055959]
+	GetHandleVerifier [0x0x7ff7eb78cfee+191102]
+	GetHandleVerifier [0x0x7ff7eb7950af+224063]
+	GetHandleVerifier [0x0x7ff7eb77af64+117236]
+	GetHandleVerifier [0x0x7ff7eb77b119+117673]
+	GetHandleVerifier [0x0x7ff7eb7610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1305,17 +1305,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£25.15</t>
+          <t>£24.86</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£25.15</t>
+          <t>£24.86</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£25.15</t>
+          <t>£24.86</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1353,25 +1353,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff69a3d1eb5+80197]
-	GetHandleVerifier [0x0x7ff69a3d1f10+80288]
-	(No symbol) [0x0x7ff69a1502fa]
-	(No symbol) [0x0x7ff69a1a7cd7]
-	(No symbol) [0x0x7ff69a1a7f9c]
-	(No symbol) [0x0x7ff69a1fba87]
-	(No symbol) [0x0x7ff69a1d03bf]
-	(No symbol) [0x0x7ff69a1f87fb]
-	(No symbol) [0x0x7ff69a1d0153]
-	(No symbol) [0x0x7ff69a198b02]
-	(No symbol) [0x0x7ff69a1998d3]
-	GetHandleVerifier [0x0x7ff69a68e83d+2949837]
-	GetHandleVerifier [0x0x7ff69a688c6a+2926330]
-	GetHandleVerifier [0x0x7ff69a6a86c7+3055959]
-	GetHandleVerifier [0x0x7ff69a3ecfee+191102]
-	GetHandleVerifier [0x0x7ff69a3f50af+224063]
-	GetHandleVerifier [0x0x7ff69a3daf64+117236]
-	GetHandleVerifier [0x0x7ff69a3db119+117673]
-	GetHandleVerifier [0x0x7ff69a3c10a8+11064]
+	GetHandleVerifier [0x0x7ff7eb771eb5+80197]
+	GetHandleVerifier [0x0x7ff7eb771f10+80288]
+	(No symbol) [0x0x7ff7eb4f02fa]
+	(No symbol) [0x0x7ff7eb547cd7]
+	(No symbol) [0x0x7ff7eb547f9c]
+	(No symbol) [0x0x7ff7eb59ba87]
+	(No symbol) [0x0x7ff7eb5703bf]
+	(No symbol) [0x0x7ff7eb5987fb]
+	(No symbol) [0x0x7ff7eb570153]
+	(No symbol) [0x0x7ff7eb538b02]
+	(No symbol) [0x0x7ff7eb5398d3]
+	GetHandleVerifier [0x0x7ff7eba2e83d+2949837]
+	GetHandleVerifier [0x0x7ff7eba28c6a+2926330]
+	GetHandleVerifier [0x0x7ff7eba486c7+3055959]
+	GetHandleVerifier [0x0x7ff7eb78cfee+191102]
+	GetHandleVerifier [0x0x7ff7eb7950af+224063]
+	GetHandleVerifier [0x0x7ff7eb77af64+117236]
+	GetHandleVerifier [0x0x7ff7eb77b119+117673]
+	GetHandleVerifier [0x0x7ff7eb7610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1416,17 +1416,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£27.25</t>
+          <t>£26.95</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£27.25</t>
+          <t>£26.95</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£27.25</t>
+          <t>£26.95</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1464,25 +1464,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff69a3d1eb5+80197]
-	GetHandleVerifier [0x0x7ff69a3d1f10+80288]
-	(No symbol) [0x0x7ff69a1502fa]
-	(No symbol) [0x0x7ff69a1a7cd7]
-	(No symbol) [0x0x7ff69a1a7f9c]
-	(No symbol) [0x0x7ff69a1fba87]
-	(No symbol) [0x0x7ff69a1d03bf]
-	(No symbol) [0x0x7ff69a1f87fb]
-	(No symbol) [0x0x7ff69a1d0153]
-	(No symbol) [0x0x7ff69a198b02]
-	(No symbol) [0x0x7ff69a1998d3]
-	GetHandleVerifier [0x0x7ff69a68e83d+2949837]
-	GetHandleVerifier [0x0x7ff69a688c6a+2926330]
-	GetHandleVerifier [0x0x7ff69a6a86c7+3055959]
-	GetHandleVerifier [0x0x7ff69a3ecfee+191102]
-	GetHandleVerifier [0x0x7ff69a3f50af+224063]
-	GetHandleVerifier [0x0x7ff69a3daf64+117236]
-	GetHandleVerifier [0x0x7ff69a3db119+117673]
-	GetHandleVerifier [0x0x7ff69a3c10a8+11064]
+	GetHandleVerifier [0x0x7ff7eb771eb5+80197]
+	GetHandleVerifier [0x0x7ff7eb771f10+80288]
+	(No symbol) [0x0x7ff7eb4f02fa]
+	(No symbol) [0x0x7ff7eb547cd7]
+	(No symbol) [0x0x7ff7eb547f9c]
+	(No symbol) [0x0x7ff7eb59ba87]
+	(No symbol) [0x0x7ff7eb5703bf]
+	(No symbol) [0x0x7ff7eb5987fb]
+	(No symbol) [0x0x7ff7eb570153]
+	(No symbol) [0x0x7ff7eb538b02]
+	(No symbol) [0x0x7ff7eb5398d3]
+	GetHandleVerifier [0x0x7ff7eba2e83d+2949837]
+	GetHandleVerifier [0x0x7ff7eba28c6a+2926330]
+	GetHandleVerifier [0x0x7ff7eba486c7+3055959]
+	GetHandleVerifier [0x0x7ff7eb78cfee+191102]
+	GetHandleVerifier [0x0x7ff7eb7950af+224063]
+	GetHandleVerifier [0x0x7ff7eb77af64+117236]
+	GetHandleVerifier [0x0x7ff7eb77b119+117673]
+	GetHandleVerifier [0x0x7ff7eb7610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1527,17 +1527,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£26.79</t>
+          <t>£26.50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£26.79</t>
+          <t>£26.50</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£26.79</t>
+          <t>£26.50</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1575,25 +1575,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff69a3d1eb5+80197]
-	GetHandleVerifier [0x0x7ff69a3d1f10+80288]
-	(No symbol) [0x0x7ff69a1502fa]
-	(No symbol) [0x0x7ff69a1a7cd7]
-	(No symbol) [0x0x7ff69a1a7f9c]
-	(No symbol) [0x0x7ff69a1fba87]
-	(No symbol) [0x0x7ff69a1d03bf]
-	(No symbol) [0x0x7ff69a1f87fb]
-	(No symbol) [0x0x7ff69a1d0153]
-	(No symbol) [0x0x7ff69a198b02]
-	(No symbol) [0x0x7ff69a1998d3]
-	GetHandleVerifier [0x0x7ff69a68e83d+2949837]
-	GetHandleVerifier [0x0x7ff69a688c6a+2926330]
-	GetHandleVerifier [0x0x7ff69a6a86c7+3055959]
-	GetHandleVerifier [0x0x7ff69a3ecfee+191102]
-	GetHandleVerifier [0x0x7ff69a3f50af+224063]
-	GetHandleVerifier [0x0x7ff69a3daf64+117236]
-	GetHandleVerifier [0x0x7ff69a3db119+117673]
-	GetHandleVerifier [0x0x7ff69a3c10a8+11064]
+	GetHandleVerifier [0x0x7ff7eb771eb5+80197]
+	GetHandleVerifier [0x0x7ff7eb771f10+80288]
+	(No symbol) [0x0x7ff7eb4f02fa]
+	(No symbol) [0x0x7ff7eb547cd7]
+	(No symbol) [0x0x7ff7eb547f9c]
+	(No symbol) [0x0x7ff7eb59ba87]
+	(No symbol) [0x0x7ff7eb5703bf]
+	(No symbol) [0x0x7ff7eb5987fb]
+	(No symbol) [0x0x7ff7eb570153]
+	(No symbol) [0x0x7ff7eb538b02]
+	(No symbol) [0x0x7ff7eb5398d3]
+	GetHandleVerifier [0x0x7ff7eba2e83d+2949837]
+	GetHandleVerifier [0x0x7ff7eba28c6a+2926330]
+	GetHandleVerifier [0x0x7ff7eba486c7+3055959]
+	GetHandleVerifier [0x0x7ff7eb78cfee+191102]
+	GetHandleVerifier [0x0x7ff7eb7950af+224063]
+	GetHandleVerifier [0x0x7ff7eb77af64+117236]
+	GetHandleVerifier [0x0x7ff7eb77b119+117673]
+	GetHandleVerifier [0x0x7ff7eb7610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1686,25 +1686,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff69a3d1eb5+80197]
-	GetHandleVerifier [0x0x7ff69a3d1f10+80288]
-	(No symbol) [0x0x7ff69a1502fa]
-	(No symbol) [0x0x7ff69a1a7cd7]
-	(No symbol) [0x0x7ff69a1a7f9c]
-	(No symbol) [0x0x7ff69a1fba87]
-	(No symbol) [0x0x7ff69a1d03bf]
-	(No symbol) [0x0x7ff69a1f87fb]
-	(No symbol) [0x0x7ff69a1d0153]
-	(No symbol) [0x0x7ff69a198b02]
-	(No symbol) [0x0x7ff69a1998d3]
-	GetHandleVerifier [0x0x7ff69a68e83d+2949837]
-	GetHandleVerifier [0x0x7ff69a688c6a+2926330]
-	GetHandleVerifier [0x0x7ff69a6a86c7+3055959]
-	GetHandleVerifier [0x0x7ff69a3ecfee+191102]
-	GetHandleVerifier [0x0x7ff69a3f50af+224063]
-	GetHandleVerifier [0x0x7ff69a3daf64+117236]
-	GetHandleVerifier [0x0x7ff69a3db119+117673]
-	GetHandleVerifier [0x0x7ff69a3c10a8+11064]
+	GetHandleVerifier [0x0x7ff7eb771eb5+80197]
+	GetHandleVerifier [0x0x7ff7eb771f10+80288]
+	(No symbol) [0x0x7ff7eb4f02fa]
+	(No symbol) [0x0x7ff7eb547cd7]
+	(No symbol) [0x0x7ff7eb547f9c]
+	(No symbol) [0x0x7ff7eb59ba87]
+	(No symbol) [0x0x7ff7eb5703bf]
+	(No symbol) [0x0x7ff7eb5987fb]
+	(No symbol) [0x0x7ff7eb570153]
+	(No symbol) [0x0x7ff7eb538b02]
+	(No symbol) [0x0x7ff7eb5398d3]
+	GetHandleVerifier [0x0x7ff7eba2e83d+2949837]
+	GetHandleVerifier [0x0x7ff7eba28c6a+2926330]
+	GetHandleVerifier [0x0x7ff7eba486c7+3055959]
+	GetHandleVerifier [0x0x7ff7eb78cfee+191102]
+	GetHandleVerifier [0x0x7ff7eb7950af+224063]
+	GetHandleVerifier [0x0x7ff7eb77af64+117236]
+	GetHandleVerifier [0x0x7ff7eb77b119+117673]
+	GetHandleVerifier [0x0x7ff7eb7610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1749,17 +1749,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£32.89</t>
+          <t>£32.49</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£32.89</t>
+          <t>£32.49</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£32.89</t>
+          <t>£32.49</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1797,25 +1797,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff69a3d1eb5+80197]
-	GetHandleVerifier [0x0x7ff69a3d1f10+80288]
-	(No symbol) [0x0x7ff69a1502fa]
-	(No symbol) [0x0x7ff69a1a7cd7]
-	(No symbol) [0x0x7ff69a1a7f9c]
-	(No symbol) [0x0x7ff69a1fba87]
-	(No symbol) [0x0x7ff69a1d03bf]
-	(No symbol) [0x0x7ff69a1f87fb]
-	(No symbol) [0x0x7ff69a1d0153]
-	(No symbol) [0x0x7ff69a198b02]
-	(No symbol) [0x0x7ff69a1998d3]
-	GetHandleVerifier [0x0x7ff69a68e83d+2949837]
-	GetHandleVerifier [0x0x7ff69a688c6a+2926330]
-	GetHandleVerifier [0x0x7ff69a6a86c7+3055959]
-	GetHandleVerifier [0x0x7ff69a3ecfee+191102]
-	GetHandleVerifier [0x0x7ff69a3f50af+224063]
-	GetHandleVerifier [0x0x7ff69a3daf64+117236]
-	GetHandleVerifier [0x0x7ff69a3db119+117673]
-	GetHandleVerifier [0x0x7ff69a3c10a8+11064]
+	GetHandleVerifier [0x0x7ff7eb771eb5+80197]
+	GetHandleVerifier [0x0x7ff7eb771f10+80288]
+	(No symbol) [0x0x7ff7eb4f02fa]
+	(No symbol) [0x0x7ff7eb547cd7]
+	(No symbol) [0x0x7ff7eb547f9c]
+	(No symbol) [0x0x7ff7eb59ba87]
+	(No symbol) [0x0x7ff7eb5703bf]
+	(No symbol) [0x0x7ff7eb5987fb]
+	(No symbol) [0x0x7ff7eb570153]
+	(No symbol) [0x0x7ff7eb538b02]
+	(No symbol) [0x0x7ff7eb5398d3]
+	GetHandleVerifier [0x0x7ff7eba2e83d+2949837]
+	GetHandleVerifier [0x0x7ff7eba28c6a+2926330]
+	GetHandleVerifier [0x0x7ff7eba486c7+3055959]
+	GetHandleVerifier [0x0x7ff7eb78cfee+191102]
+	GetHandleVerifier [0x0x7ff7eb7950af+224063]
+	GetHandleVerifier [0x0x7ff7eb77af64+117236]
+	GetHandleVerifier [0x0x7ff7eb77b119+117673]
+	GetHandleVerifier [0x0x7ff7eb7610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1860,17 +1860,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£40.15</t>
+          <t>£39.76</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£40.15</t>
+          <t>£39.76</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£40.15</t>
+          <t>£39.76</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1908,25 +1908,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff69a3d1eb5+80197]
-	GetHandleVerifier [0x0x7ff69a3d1f10+80288]
-	(No symbol) [0x0x7ff69a1502fa]
-	(No symbol) [0x0x7ff69a1a7cd7]
-	(No symbol) [0x0x7ff69a1a7f9c]
-	(No symbol) [0x0x7ff69a1fba87]
-	(No symbol) [0x0x7ff69a1d03bf]
-	(No symbol) [0x0x7ff69a1f87fb]
-	(No symbol) [0x0x7ff69a1d0153]
-	(No symbol) [0x0x7ff69a198b02]
-	(No symbol) [0x0x7ff69a1998d3]
-	GetHandleVerifier [0x0x7ff69a68e83d+2949837]
-	GetHandleVerifier [0x0x7ff69a688c6a+2926330]
-	GetHandleVerifier [0x0x7ff69a6a86c7+3055959]
-	GetHandleVerifier [0x0x7ff69a3ecfee+191102]
-	GetHandleVerifier [0x0x7ff69a3f50af+224063]
-	GetHandleVerifier [0x0x7ff69a3daf64+117236]
-	GetHandleVerifier [0x0x7ff69a3db119+117673]
-	GetHandleVerifier [0x0x7ff69a3c10a8+11064]
+	GetHandleVerifier [0x0x7ff7eb771eb5+80197]
+	GetHandleVerifier [0x0x7ff7eb771f10+80288]
+	(No symbol) [0x0x7ff7eb4f02fa]
+	(No symbol) [0x0x7ff7eb547cd7]
+	(No symbol) [0x0x7ff7eb547f9c]
+	(No symbol) [0x0x7ff7eb59ba87]
+	(No symbol) [0x0x7ff7eb5703bf]
+	(No symbol) [0x0x7ff7eb5987fb]
+	(No symbol) [0x0x7ff7eb570153]
+	(No symbol) [0x0x7ff7eb538b02]
+	(No symbol) [0x0x7ff7eb5398d3]
+	GetHandleVerifier [0x0x7ff7eba2e83d+2949837]
+	GetHandleVerifier [0x0x7ff7eba28c6a+2926330]
+	GetHandleVerifier [0x0x7ff7eba486c7+3055959]
+	GetHandleVerifier [0x0x7ff7eb78cfee+191102]
+	GetHandleVerifier [0x0x7ff7eb7950af+224063]
+	GetHandleVerifier [0x0x7ff7eb77af64+117236]
+	GetHandleVerifier [0x0x7ff7eb77b119+117673]
+	GetHandleVerifier [0x0x7ff7eb7610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1971,17 +1971,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£40.95</t>
+          <t>£40.39</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£40.95</t>
+          <t>£40.39</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>£40.95</t>
+          <t>£40.39</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2019,25 +2019,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff69a3d1eb5+80197]
-	GetHandleVerifier [0x0x7ff69a3d1f10+80288]
-	(No symbol) [0x0x7ff69a1502fa]
-	(No symbol) [0x0x7ff69a1a7cd7]
-	(No symbol) [0x0x7ff69a1a7f9c]
-	(No symbol) [0x0x7ff69a1fba87]
-	(No symbol) [0x0x7ff69a1d03bf]
-	(No symbol) [0x0x7ff69a1f87fb]
-	(No symbol) [0x0x7ff69a1d0153]
-	(No symbol) [0x0x7ff69a198b02]
-	(No symbol) [0x0x7ff69a1998d3]
-	GetHandleVerifier [0x0x7ff69a68e83d+2949837]
-	GetHandleVerifier [0x0x7ff69a688c6a+2926330]
-	GetHandleVerifier [0x0x7ff69a6a86c7+3055959]
-	GetHandleVerifier [0x0x7ff69a3ecfee+191102]
-	GetHandleVerifier [0x0x7ff69a3f50af+224063]
-	GetHandleVerifier [0x0x7ff69a3daf64+117236]
-	GetHandleVerifier [0x0x7ff69a3db119+117673]
-	GetHandleVerifier [0x0x7ff69a3c10a8+11064]
+	GetHandleVerifier [0x0x7ff7eb771eb5+80197]
+	GetHandleVerifier [0x0x7ff7eb771f10+80288]
+	(No symbol) [0x0x7ff7eb4f02fa]
+	(No symbol) [0x0x7ff7eb547cd7]
+	(No symbol) [0x0x7ff7eb547f9c]
+	(No symbol) [0x0x7ff7eb59ba87]
+	(No symbol) [0x0x7ff7eb5703bf]
+	(No symbol) [0x0x7ff7eb5987fb]
+	(No symbol) [0x0x7ff7eb570153]
+	(No symbol) [0x0x7ff7eb538b02]
+	(No symbol) [0x0x7ff7eb5398d3]
+	GetHandleVerifier [0x0x7ff7eba2e83d+2949837]
+	GetHandleVerifier [0x0x7ff7eba28c6a+2926330]
+	GetHandleVerifier [0x0x7ff7eba486c7+3055959]
+	GetHandleVerifier [0x0x7ff7eb78cfee+191102]
+	GetHandleVerifier [0x0x7ff7eb7950af+224063]
+	GetHandleVerifier [0x0x7ff7eb77af64+117236]
+	GetHandleVerifier [0x0x7ff7eb77b119+117673]
+	GetHandleVerifier [0x0x7ff7eb7610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2082,17 +2082,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£40.85</t>
+          <t>£40.45</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£40.85</t>
+          <t>£40.45</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£40.85</t>
+          <t>£40.45</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2130,25 +2130,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff69a3d1eb5+80197]
-	GetHandleVerifier [0x0x7ff69a3d1f10+80288]
-	(No symbol) [0x0x7ff69a1502fa]
-	(No symbol) [0x0x7ff69a1a7cd7]
-	(No symbol) [0x0x7ff69a1a7f9c]
-	(No symbol) [0x0x7ff69a1fba87]
-	(No symbol) [0x0x7ff69a1d03bf]
-	(No symbol) [0x0x7ff69a1f87fb]
-	(No symbol) [0x0x7ff69a1d0153]
-	(No symbol) [0x0x7ff69a198b02]
-	(No symbol) [0x0x7ff69a1998d3]
-	GetHandleVerifier [0x0x7ff69a68e83d+2949837]
-	GetHandleVerifier [0x0x7ff69a688c6a+2926330]
-	GetHandleVerifier [0x0x7ff69a6a86c7+3055959]
-	GetHandleVerifier [0x0x7ff69a3ecfee+191102]
-	GetHandleVerifier [0x0x7ff69a3f50af+224063]
-	GetHandleVerifier [0x0x7ff69a3daf64+117236]
-	GetHandleVerifier [0x0x7ff69a3db119+117673]
-	GetHandleVerifier [0x0x7ff69a3c10a8+11064]
+	GetHandleVerifier [0x0x7ff7eb771eb5+80197]
+	GetHandleVerifier [0x0x7ff7eb771f10+80288]
+	(No symbol) [0x0x7ff7eb4f02fa]
+	(No symbol) [0x0x7ff7eb547cd7]
+	(No symbol) [0x0x7ff7eb547f9c]
+	(No symbol) [0x0x7ff7eb59ba87]
+	(No symbol) [0x0x7ff7eb5703bf]
+	(No symbol) [0x0x7ff7eb5987fb]
+	(No symbol) [0x0x7ff7eb570153]
+	(No symbol) [0x0x7ff7eb538b02]
+	(No symbol) [0x0x7ff7eb5398d3]
+	GetHandleVerifier [0x0x7ff7eba2e83d+2949837]
+	GetHandleVerifier [0x0x7ff7eba28c6a+2926330]
+	GetHandleVerifier [0x0x7ff7eba486c7+3055959]
+	GetHandleVerifier [0x0x7ff7eb78cfee+191102]
+	GetHandleVerifier [0x0x7ff7eb7950af+224063]
+	GetHandleVerifier [0x0x7ff7eb77af64+117236]
+	GetHandleVerifier [0x0x7ff7eb77b119+117673]
+	GetHandleVerifier [0x0x7ff7eb7610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
